--- a/Documents/Interface_Specification/Interface.xlsx
+++ b/Documents/Interface_Specification/Interface.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded_work\PROJECTS\PIR_Security_Node\Firmware\Interface_Specification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded_work\PROJECTS\PIR_Security_Node\Documents\Interface_Specification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9238214-071A-43A2-B463-72272AEE70E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49187FF-2B91-420D-BCEF-E4AAD7258DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3048" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Interface</t>
   </si>
@@ -100,6 +100,15 @@
   </si>
   <si>
     <t>PA10</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>PC13</t>
+  </si>
+  <si>
+    <t>INDICATION</t>
   </si>
 </sst>
 </file>
@@ -431,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -543,6 +552,23 @@
         <v>22</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
